--- a/builds/Summary stats.xlsx
+++ b/builds/Summary stats.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ejlundgren/Dropbox/Projects/iucn_evidence/CATS/builds/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ejlundgren/Dropbox/Projects/iucn_evidence/cat_evidence_review/builds/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9AB60BD6-CA54-2447-8A66-BFAAC01145F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C209679A-6D1A-6C47-9409-73BB53A0E66B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="17920" activeTab="1" xr2:uid="{8797134B-E1C8-964D-BC69-1A0334CFECDC}"/>
   </bookViews>
@@ -376,7 +376,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="851" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="852" uniqueCount="70">
   <si>
     <t>Number</t>
   </si>
@@ -583,6 +583,9 @@
   </si>
   <si>
     <t>66.7% ±42.49</t>
+  </si>
+  <si>
+    <t>&lt;- I think this is the one that changed</t>
   </si>
 </sst>
 </file>
@@ -785,7 +788,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -858,6 +861,9 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -3516,6 +3522,7 @@
     <sortCondition ref="A14:A19"/>
   </sortState>
   <mergeCells count="17">
+    <mergeCell ref="K52:L52"/>
     <mergeCell ref="K68:L68"/>
     <mergeCell ref="A1:L1"/>
     <mergeCell ref="H2:I2"/>
@@ -3532,7 +3539,6 @@
     <mergeCell ref="B52:C52"/>
     <mergeCell ref="K2:L2"/>
     <mergeCell ref="K36:L36"/>
-    <mergeCell ref="K52:L52"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3545,7 +3551,7 @@
   <cols>
     <col min="1" max="1" width="45.83203125" style="2" customWidth="1"/>
     <col min="2" max="2" width="29.33203125" style="5" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="24.33203125" style="5" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="35" style="5" customWidth="1"/>
     <col min="4" max="4" width="50.5" style="5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -3592,8 +3598,8 @@
       <c r="A5" s="9" t="s">
         <v>41</v>
       </c>
-      <c r="B5" s="4">
-        <v>727</v>
+      <c r="B5" s="21">
+        <v>728</v>
       </c>
       <c r="C5" s="3"/>
       <c r="D5" s="3"/>
@@ -3602,8 +3608,8 @@
       <c r="A6" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="B6" s="4">
-        <v>310</v>
+      <c r="B6" s="21">
+        <v>309</v>
       </c>
       <c r="C6" s="3"/>
       <c r="D6" s="3"/>
@@ -3612,8 +3618,8 @@
       <c r="A7" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="B7" s="4">
-        <v>473</v>
+      <c r="B7" s="21">
+        <v>472</v>
       </c>
       <c r="C7" s="3"/>
       <c r="D7" s="3"/>
@@ -3670,10 +3676,12 @@
       <c r="A13" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="B13" s="4">
-        <v>49</v>
-      </c>
-      <c r="C13" s="3"/>
+      <c r="B13" s="21">
+        <v>48</v>
+      </c>
+      <c r="C13" s="21" t="s">
+        <v>69</v>
+      </c>
       <c r="D13" s="3"/>
       <c r="E13" s="20" t="s">
         <v>52</v>
@@ -3872,8 +3880,8 @@
       <c r="A32" s="9" t="s">
         <v>41</v>
       </c>
-      <c r="B32" s="4">
-        <v>311</v>
+      <c r="B32" s="21">
+        <v>312</v>
       </c>
       <c r="C32" s="3"/>
       <c r="D32" s="3"/>
@@ -4224,10 +4232,10 @@
       <c r="A67" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="B67" s="4">
-        <v>36</v>
-      </c>
-      <c r="C67" s="3"/>
+      <c r="B67" s="21">
+        <v>35</v>
+      </c>
+      <c r="C67" s="26"/>
       <c r="D67" s="3"/>
     </row>
     <row r="68" spans="1:4" ht="17" x14ac:dyDescent="0.2">
